--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97512</v>
+        <v>97518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97518</v>
+        <v>97519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97519</v>
+        <v>97523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97523</v>
+        <v>97525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97525</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97534</v>
+        <v>97542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97542</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97543</v>
+        <v>97512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127284796</v>
       </c>
       <c r="B2" t="n">
-        <v>97512</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127284796</v>
+        <v>87107549</v>
       </c>
       <c r="B2" t="n">
-        <v>97543</v>
+        <v>96004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>1132</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Parkhättemossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Orthotrichum pallens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Bruch ex Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>300 m S om Dalsta gård, Dalsta, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660521</v>
+        <v>660564</v>
       </c>
       <c r="R2" t="n">
-        <v>6556289</v>
+        <v>6556324</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kollekt, ev. var arnellii, har 16 inre peristom och växer på block</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,32 +759,539 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>I gles lövskog 10-20 meter väster om Kagghamraån.</t>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>block nedanför al vid å</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander, Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>87107536</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97812</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2605</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stenporella</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porella cordaeana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Huebener) Moore</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>660527</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6556312</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander, Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87107534</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>660510</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6556310</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander, Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>87107533</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>660510</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6556310</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander, Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87107537</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>660527</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6556312</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-07-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander, Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127284796</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>300 m S om Dalsta gård, Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>660521</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6556289</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>I gles lövskog 10-20 meter väster om Kagghamraån.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Britta Ahlgren</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Britta Ahlgren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33801-2025 artfynd.xlsx
+++ b/artfynd/A 33801-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87107549</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87107536</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87107534</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87107533</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,6 +1193,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87107537</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,8 +1322,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127284796</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>